--- a/analyses/trees/RNA1/RNA1_Seq_IDs.xlsx
+++ b/analyses/trees/RNA1/RNA1_Seq_IDs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/diverse_collections/github/analyses/trees/RNA1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4BE628-9C81-194B-A57F-824DC498BF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5FE7A4-D92B-724D-A1F9-272A3581F143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32400" yWindow="500" windowWidth="17240" windowHeight="21100" xr2:uid="{C5CC4E02-00F2-344F-A047-B9E9E3AD013B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="285">
   <si>
     <t>D_mel_USA_2020_mel-20-TD-3_Galbut_virus_RNA1_Complete_CDS</t>
   </si>
@@ -840,6 +840,57 @@
   </si>
   <si>
     <t>simulans</t>
+  </si>
+  <si>
+    <t>street</t>
+  </si>
+  <si>
+    <t>Linden</t>
+  </si>
+  <si>
+    <t>Wabash</t>
+  </si>
+  <si>
+    <t>Elm</t>
+  </si>
+  <si>
+    <t>Adobe</t>
+  </si>
+  <si>
+    <t>Briarwood</t>
+  </si>
+  <si>
+    <t>Rampart</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Cushman</t>
+  </si>
+  <si>
+    <t>Myrtle</t>
+  </si>
+  <si>
+    <t>Williamsburg</t>
+  </si>
+  <si>
+    <t>JFK Parkway</t>
+  </si>
+  <si>
+    <t>Toftrees</t>
+  </si>
+  <si>
+    <t>Cushmab</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Laurel</t>
+  </si>
+  <si>
+    <t>Michener</t>
   </si>
 </sst>
 </file>
@@ -1211,15 +1262,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{395C2393-5C50-2A47-93A3-2BB7B4877225}">
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:F153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>251</v>
       </c>
@@ -1230,13 +1281,16 @@
         <v>249</v>
       </c>
       <c r="D1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" t="s">
         <v>262</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1246,14 +1300,17 @@
       <c r="C2" t="s">
         <v>253</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2">
         <v>2020</v>
       </c>
-      <c r="E2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1263,14 +1320,17 @@
       <c r="C3" t="s">
         <v>253</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3">
         <v>2020</v>
       </c>
-      <c r="E3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1280,14 +1340,17 @@
       <c r="C4" t="s">
         <v>253</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E4">
         <v>2021</v>
       </c>
-      <c r="E4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1297,14 +1360,17 @@
       <c r="C5" t="s">
         <v>253</v>
       </c>
-      <c r="D5">
-        <v>2023</v>
-      </c>
-      <c r="E5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5">
+        <v>2023</v>
+      </c>
+      <c r="F5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1314,14 +1380,17 @@
       <c r="C6" t="s">
         <v>253</v>
       </c>
-      <c r="D6">
-        <v>2023</v>
-      </c>
-      <c r="E6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6">
+        <v>2023</v>
+      </c>
+      <c r="F6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1331,14 +1400,17 @@
       <c r="C7" t="s">
         <v>253</v>
       </c>
-      <c r="D7">
-        <v>2023</v>
-      </c>
-      <c r="E7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E7">
+        <v>2023</v>
+      </c>
+      <c r="F7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1348,14 +1420,17 @@
       <c r="C8" t="s">
         <v>253</v>
       </c>
-      <c r="D8">
-        <v>2023</v>
-      </c>
-      <c r="E8" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>269</v>
+      </c>
+      <c r="E8">
+        <v>2023</v>
+      </c>
+      <c r="F8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1365,14 +1440,17 @@
       <c r="C9" t="s">
         <v>253</v>
       </c>
-      <c r="D9">
-        <v>2023</v>
-      </c>
-      <c r="E9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E9">
+        <v>2023</v>
+      </c>
+      <c r="F9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1382,14 +1460,17 @@
       <c r="C10" t="s">
         <v>253</v>
       </c>
-      <c r="D10">
-        <v>2023</v>
-      </c>
-      <c r="E10" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D10" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10">
+        <v>2023</v>
+      </c>
+      <c r="F10" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1399,14 +1480,17 @@
       <c r="C11" t="s">
         <v>253</v>
       </c>
-      <c r="D11">
-        <v>2023</v>
-      </c>
-      <c r="E11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E11">
+        <v>2023</v>
+      </c>
+      <c r="F11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1416,14 +1500,17 @@
       <c r="C12" t="s">
         <v>253</v>
       </c>
-      <c r="D12">
-        <v>2023</v>
-      </c>
-      <c r="E12" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E12">
+        <v>2023</v>
+      </c>
+      <c r="F12" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1433,14 +1520,17 @@
       <c r="C13" t="s">
         <v>253</v>
       </c>
-      <c r="D13">
-        <v>2023</v>
-      </c>
-      <c r="E13" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D13" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13">
+        <v>2023</v>
+      </c>
+      <c r="F13" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1450,14 +1540,17 @@
       <c r="C14" t="s">
         <v>253</v>
       </c>
-      <c r="D14">
-        <v>2023</v>
-      </c>
-      <c r="E14" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D14" t="s">
+        <v>269</v>
+      </c>
+      <c r="E14">
+        <v>2023</v>
+      </c>
+      <c r="F14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1467,14 +1560,17 @@
       <c r="C15" t="s">
         <v>253</v>
       </c>
-      <c r="D15">
-        <v>2023</v>
-      </c>
-      <c r="E15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D15" t="s">
+        <v>269</v>
+      </c>
+      <c r="E15">
+        <v>2023</v>
+      </c>
+      <c r="F15" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1484,14 +1580,17 @@
       <c r="C16" t="s">
         <v>253</v>
       </c>
-      <c r="D16">
-        <v>2023</v>
-      </c>
-      <c r="E16" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D16" t="s">
+        <v>269</v>
+      </c>
+      <c r="E16">
+        <v>2023</v>
+      </c>
+      <c r="F16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1501,14 +1600,17 @@
       <c r="C17" t="s">
         <v>253</v>
       </c>
-      <c r="D17">
-        <v>2023</v>
-      </c>
-      <c r="E17" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D17" t="s">
+        <v>269</v>
+      </c>
+      <c r="E17">
+        <v>2023</v>
+      </c>
+      <c r="F17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1518,14 +1620,17 @@
       <c r="C18" t="s">
         <v>253</v>
       </c>
-      <c r="D18">
-        <v>2023</v>
-      </c>
-      <c r="E18" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D18" t="s">
+        <v>269</v>
+      </c>
+      <c r="E18">
+        <v>2023</v>
+      </c>
+      <c r="F18" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1535,14 +1640,17 @@
       <c r="C19" t="s">
         <v>253</v>
       </c>
-      <c r="D19">
-        <v>2023</v>
-      </c>
-      <c r="E19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D19" t="s">
+        <v>269</v>
+      </c>
+      <c r="E19">
+        <v>2023</v>
+      </c>
+      <c r="F19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1552,14 +1660,17 @@
       <c r="C20" t="s">
         <v>253</v>
       </c>
-      <c r="D20">
-        <v>2023</v>
-      </c>
-      <c r="E20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D20" t="s">
+        <v>269</v>
+      </c>
+      <c r="E20">
+        <v>2023</v>
+      </c>
+      <c r="F20" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1569,14 +1680,17 @@
       <c r="C21" t="s">
         <v>253</v>
       </c>
-      <c r="D21">
-        <v>2023</v>
-      </c>
-      <c r="E21" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D21" t="s">
+        <v>269</v>
+      </c>
+      <c r="E21">
+        <v>2023</v>
+      </c>
+      <c r="F21" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1586,14 +1700,17 @@
       <c r="C22" t="s">
         <v>253</v>
       </c>
-      <c r="D22">
-        <v>2023</v>
-      </c>
-      <c r="E22" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D22" t="s">
+        <v>269</v>
+      </c>
+      <c r="E22">
+        <v>2023</v>
+      </c>
+      <c r="F22" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -1603,14 +1720,17 @@
       <c r="C23" t="s">
         <v>253</v>
       </c>
-      <c r="D23">
-        <v>2023</v>
-      </c>
-      <c r="E23" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D23" t="s">
+        <v>269</v>
+      </c>
+      <c r="E23">
+        <v>2023</v>
+      </c>
+      <c r="F23" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1620,14 +1740,17 @@
       <c r="C24" t="s">
         <v>253</v>
       </c>
-      <c r="D24">
-        <v>2023</v>
-      </c>
-      <c r="E24" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D24" t="s">
+        <v>270</v>
+      </c>
+      <c r="E24">
+        <v>2023</v>
+      </c>
+      <c r="F24" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -1637,14 +1760,17 @@
       <c r="C25" t="s">
         <v>253</v>
       </c>
-      <c r="D25">
-        <v>2023</v>
-      </c>
-      <c r="E25" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>270</v>
+      </c>
+      <c r="E25">
+        <v>2023</v>
+      </c>
+      <c r="F25" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -1654,14 +1780,17 @@
       <c r="C26" t="s">
         <v>253</v>
       </c>
-      <c r="D26">
-        <v>2023</v>
-      </c>
-      <c r="E26" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D26" t="s">
+        <v>270</v>
+      </c>
+      <c r="E26">
+        <v>2023</v>
+      </c>
+      <c r="F26" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -1671,14 +1800,17 @@
       <c r="C27" t="s">
         <v>253</v>
       </c>
-      <c r="D27">
-        <v>2023</v>
-      </c>
-      <c r="E27" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E27">
+        <v>2023</v>
+      </c>
+      <c r="F27" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1688,14 +1820,17 @@
       <c r="C28" t="s">
         <v>253</v>
       </c>
-      <c r="D28">
-        <v>2023</v>
-      </c>
-      <c r="E28" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D28" t="s">
+        <v>270</v>
+      </c>
+      <c r="E28">
+        <v>2023</v>
+      </c>
+      <c r="F28" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -1705,14 +1840,17 @@
       <c r="C29" t="s">
         <v>253</v>
       </c>
-      <c r="D29">
-        <v>2023</v>
-      </c>
-      <c r="E29" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D29" t="s">
+        <v>270</v>
+      </c>
+      <c r="E29">
+        <v>2023</v>
+      </c>
+      <c r="F29" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -1722,14 +1860,17 @@
       <c r="C30" t="s">
         <v>253</v>
       </c>
-      <c r="D30">
-        <v>2023</v>
-      </c>
-      <c r="E30" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>270</v>
+      </c>
+      <c r="E30">
+        <v>2023</v>
+      </c>
+      <c r="F30" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -1739,14 +1880,17 @@
       <c r="C31" t="s">
         <v>253</v>
       </c>
-      <c r="D31">
-        <v>2023</v>
-      </c>
-      <c r="E31" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D31" t="s">
+        <v>270</v>
+      </c>
+      <c r="E31">
+        <v>2023</v>
+      </c>
+      <c r="F31" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -1756,14 +1900,17 @@
       <c r="C32" t="s">
         <v>253</v>
       </c>
-      <c r="D32">
-        <v>2023</v>
-      </c>
-      <c r="E32" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D32" t="s">
+        <v>270</v>
+      </c>
+      <c r="E32">
+        <v>2023</v>
+      </c>
+      <c r="F32" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -1773,14 +1920,17 @@
       <c r="C33" t="s">
         <v>253</v>
       </c>
-      <c r="D33">
-        <v>2023</v>
-      </c>
-      <c r="E33" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D33" t="s">
+        <v>270</v>
+      </c>
+      <c r="E33">
+        <v>2023</v>
+      </c>
+      <c r="F33" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -1790,14 +1940,17 @@
       <c r="C34" t="s">
         <v>253</v>
       </c>
-      <c r="D34">
-        <v>2023</v>
-      </c>
-      <c r="E34" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D34" t="s">
+        <v>270</v>
+      </c>
+      <c r="E34">
+        <v>2023</v>
+      </c>
+      <c r="F34" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -1807,14 +1960,17 @@
       <c r="C35" t="s">
         <v>253</v>
       </c>
-      <c r="D35">
-        <v>2023</v>
-      </c>
-      <c r="E35" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D35" t="s">
+        <v>270</v>
+      </c>
+      <c r="E35">
+        <v>2023</v>
+      </c>
+      <c r="F35" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1824,14 +1980,17 @@
       <c r="C36" t="s">
         <v>253</v>
       </c>
-      <c r="D36">
-        <v>2023</v>
-      </c>
-      <c r="E36" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D36" t="s">
+        <v>270</v>
+      </c>
+      <c r="E36">
+        <v>2023</v>
+      </c>
+      <c r="F36" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -1841,14 +2000,17 @@
       <c r="C37" t="s">
         <v>253</v>
       </c>
-      <c r="D37">
-        <v>2023</v>
-      </c>
-      <c r="E37" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D37" t="s">
+        <v>270</v>
+      </c>
+      <c r="E37">
+        <v>2023</v>
+      </c>
+      <c r="F37" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -1858,14 +2020,17 @@
       <c r="C38" t="s">
         <v>253</v>
       </c>
-      <c r="D38">
-        <v>2023</v>
-      </c>
-      <c r="E38" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D38" t="s">
+        <v>270</v>
+      </c>
+      <c r="E38">
+        <v>2023</v>
+      </c>
+      <c r="F38" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -1875,14 +2040,17 @@
       <c r="C39" t="s">
         <v>253</v>
       </c>
-      <c r="D39">
-        <v>2023</v>
-      </c>
-      <c r="E39" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D39" t="s">
+        <v>270</v>
+      </c>
+      <c r="E39">
+        <v>2023</v>
+      </c>
+      <c r="F39" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -1892,14 +2060,17 @@
       <c r="C40" t="s">
         <v>253</v>
       </c>
-      <c r="D40">
-        <v>2023</v>
-      </c>
-      <c r="E40" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D40" t="s">
+        <v>270</v>
+      </c>
+      <c r="E40">
+        <v>2023</v>
+      </c>
+      <c r="F40" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>78</v>
       </c>
@@ -1909,14 +2080,17 @@
       <c r="C41" t="s">
         <v>253</v>
       </c>
-      <c r="D41">
-        <v>2023</v>
-      </c>
-      <c r="E41" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D41" t="s">
+        <v>270</v>
+      </c>
+      <c r="E41">
+        <v>2023</v>
+      </c>
+      <c r="F41" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -1926,14 +2100,17 @@
       <c r="C42" t="s">
         <v>253</v>
       </c>
-      <c r="D42">
-        <v>2023</v>
-      </c>
-      <c r="E42" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D42" t="s">
+        <v>270</v>
+      </c>
+      <c r="E42">
+        <v>2023</v>
+      </c>
+      <c r="F42" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -1943,14 +2120,17 @@
       <c r="C43" t="s">
         <v>253</v>
       </c>
-      <c r="D43">
-        <v>2023</v>
-      </c>
-      <c r="E43" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D43" t="s">
+        <v>271</v>
+      </c>
+      <c r="E43">
+        <v>2023</v>
+      </c>
+      <c r="F43" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>84</v>
       </c>
@@ -1960,14 +2140,17 @@
       <c r="C44" t="s">
         <v>253</v>
       </c>
-      <c r="D44">
-        <v>2023</v>
-      </c>
-      <c r="E44" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D44" t="s">
+        <v>271</v>
+      </c>
+      <c r="E44">
+        <v>2023</v>
+      </c>
+      <c r="F44" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -1977,14 +2160,17 @@
       <c r="C45" t="s">
         <v>253</v>
       </c>
-      <c r="D45">
-        <v>2023</v>
-      </c>
-      <c r="E45" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D45" t="s">
+        <v>271</v>
+      </c>
+      <c r="E45">
+        <v>2023</v>
+      </c>
+      <c r="F45" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -1994,14 +2180,17 @@
       <c r="C46" t="s">
         <v>253</v>
       </c>
-      <c r="D46">
-        <v>2023</v>
-      </c>
-      <c r="E46" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D46" t="s">
+        <v>271</v>
+      </c>
+      <c r="E46">
+        <v>2023</v>
+      </c>
+      <c r="F46" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>90</v>
       </c>
@@ -2011,14 +2200,17 @@
       <c r="C47" t="s">
         <v>253</v>
       </c>
-      <c r="D47">
-        <v>2023</v>
-      </c>
-      <c r="E47" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D47" t="s">
+        <v>271</v>
+      </c>
+      <c r="E47">
+        <v>2023</v>
+      </c>
+      <c r="F47" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -2028,14 +2220,17 @@
       <c r="C48" t="s">
         <v>253</v>
       </c>
-      <c r="D48">
-        <v>2023</v>
-      </c>
-      <c r="E48" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D48" t="s">
+        <v>271</v>
+      </c>
+      <c r="E48">
+        <v>2023</v>
+      </c>
+      <c r="F48" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2045,14 +2240,17 @@
       <c r="C49" t="s">
         <v>253</v>
       </c>
-      <c r="D49">
-        <v>2023</v>
-      </c>
-      <c r="E49" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D49" t="s">
+        <v>272</v>
+      </c>
+      <c r="E49">
+        <v>2023</v>
+      </c>
+      <c r="F49" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -2062,14 +2260,17 @@
       <c r="C50" t="s">
         <v>253</v>
       </c>
-      <c r="D50">
-        <v>2023</v>
-      </c>
-      <c r="E50" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D50" t="s">
+        <v>272</v>
+      </c>
+      <c r="E50">
+        <v>2023</v>
+      </c>
+      <c r="F50" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -2079,14 +2280,17 @@
       <c r="C51" t="s">
         <v>253</v>
       </c>
-      <c r="D51">
-        <v>2023</v>
-      </c>
-      <c r="E51" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D51" t="s">
+        <v>272</v>
+      </c>
+      <c r="E51">
+        <v>2023</v>
+      </c>
+      <c r="F51" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -2096,14 +2300,17 @@
       <c r="C52" t="s">
         <v>253</v>
       </c>
-      <c r="D52">
-        <v>2023</v>
-      </c>
-      <c r="E52" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D52" t="s">
+        <v>272</v>
+      </c>
+      <c r="E52">
+        <v>2023</v>
+      </c>
+      <c r="F52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>102</v>
       </c>
@@ -2113,14 +2320,17 @@
       <c r="C53" t="s">
         <v>253</v>
       </c>
-      <c r="D53">
-        <v>2023</v>
-      </c>
-      <c r="E53" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D53" t="s">
+        <v>273</v>
+      </c>
+      <c r="E53">
+        <v>2023</v>
+      </c>
+      <c r="F53" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2130,14 +2340,17 @@
       <c r="C54" t="s">
         <v>253</v>
       </c>
-      <c r="D54">
-        <v>2023</v>
-      </c>
-      <c r="E54" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D54" t="s">
+        <v>274</v>
+      </c>
+      <c r="E54">
+        <v>2023</v>
+      </c>
+      <c r="F54" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -2147,14 +2360,17 @@
       <c r="C55" t="s">
         <v>253</v>
       </c>
-      <c r="D55">
-        <v>2023</v>
-      </c>
-      <c r="E55" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D55" t="s">
+        <v>274</v>
+      </c>
+      <c r="E55">
+        <v>2023</v>
+      </c>
+      <c r="F55" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -2164,14 +2380,17 @@
       <c r="C56" t="s">
         <v>253</v>
       </c>
-      <c r="D56">
-        <v>2023</v>
-      </c>
-      <c r="E56" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D56" t="s">
+        <v>274</v>
+      </c>
+      <c r="E56">
+        <v>2023</v>
+      </c>
+      <c r="F56" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -2181,14 +2400,17 @@
       <c r="C57" t="s">
         <v>253</v>
       </c>
-      <c r="D57">
-        <v>2023</v>
-      </c>
-      <c r="E57" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D57" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57">
+        <v>2023</v>
+      </c>
+      <c r="F57" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -2198,14 +2420,17 @@
       <c r="C58" t="s">
         <v>253</v>
       </c>
-      <c r="D58">
-        <v>2023</v>
-      </c>
-      <c r="E58" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D58" t="s">
+        <v>274</v>
+      </c>
+      <c r="E58">
+        <v>2023</v>
+      </c>
+      <c r="F58" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -2215,14 +2440,17 @@
       <c r="C59" t="s">
         <v>253</v>
       </c>
-      <c r="D59">
-        <v>2023</v>
-      </c>
-      <c r="E59" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D59" t="s">
+        <v>274</v>
+      </c>
+      <c r="E59">
+        <v>2023</v>
+      </c>
+      <c r="F59" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -2232,14 +2460,17 @@
       <c r="C60" t="s">
         <v>253</v>
       </c>
-      <c r="D60">
-        <v>2023</v>
-      </c>
-      <c r="E60" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D60" t="s">
+        <v>274</v>
+      </c>
+      <c r="E60">
+        <v>2023</v>
+      </c>
+      <c r="F60" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -2249,14 +2480,17 @@
       <c r="C61" t="s">
         <v>253</v>
       </c>
-      <c r="D61">
-        <v>2023</v>
-      </c>
-      <c r="E61" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D61" t="s">
+        <v>275</v>
+      </c>
+      <c r="E61">
+        <v>2023</v>
+      </c>
+      <c r="F61" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>120</v>
       </c>
@@ -2266,14 +2500,17 @@
       <c r="C62" t="s">
         <v>253</v>
       </c>
-      <c r="D62">
-        <v>2023</v>
-      </c>
-      <c r="E62" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D62" t="s">
+        <v>275</v>
+      </c>
+      <c r="E62">
+        <v>2023</v>
+      </c>
+      <c r="F62" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>122</v>
       </c>
@@ -2283,14 +2520,17 @@
       <c r="C63" t="s">
         <v>254</v>
       </c>
-      <c r="D63">
-        <v>2023</v>
-      </c>
-      <c r="E63" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D63" t="s">
+        <v>276</v>
+      </c>
+      <c r="E63">
+        <v>2023</v>
+      </c>
+      <c r="F63" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -2300,14 +2540,17 @@
       <c r="C64" t="s">
         <v>254</v>
       </c>
-      <c r="D64">
-        <v>2023</v>
-      </c>
-      <c r="E64" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D64" t="s">
+        <v>276</v>
+      </c>
+      <c r="E64">
+        <v>2023</v>
+      </c>
+      <c r="F64" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -2317,14 +2560,17 @@
       <c r="C65" t="s">
         <v>254</v>
       </c>
-      <c r="D65">
-        <v>2023</v>
-      </c>
-      <c r="E65" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D65" t="s">
+        <v>276</v>
+      </c>
+      <c r="E65">
+        <v>2023</v>
+      </c>
+      <c r="F65" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -2334,14 +2580,17 @@
       <c r="C66" t="s">
         <v>254</v>
       </c>
-      <c r="D66">
-        <v>2023</v>
-      </c>
-      <c r="E66" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D66" t="s">
+        <v>276</v>
+      </c>
+      <c r="E66">
+        <v>2023</v>
+      </c>
+      <c r="F66" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>130</v>
       </c>
@@ -2351,14 +2600,17 @@
       <c r="C67" t="s">
         <v>254</v>
       </c>
-      <c r="D67">
-        <v>2023</v>
-      </c>
-      <c r="E67" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D67" t="s">
+        <v>276</v>
+      </c>
+      <c r="E67">
+        <v>2023</v>
+      </c>
+      <c r="F67" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -2368,14 +2620,17 @@
       <c r="C68" t="s">
         <v>254</v>
       </c>
-      <c r="D68">
-        <v>2023</v>
-      </c>
-      <c r="E68" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D68" t="s">
+        <v>276</v>
+      </c>
+      <c r="E68">
+        <v>2023</v>
+      </c>
+      <c r="F68" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>134</v>
       </c>
@@ -2385,14 +2640,17 @@
       <c r="C69" t="s">
         <v>254</v>
       </c>
-      <c r="D69">
-        <v>2023</v>
-      </c>
-      <c r="E69" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D69" t="s">
+        <v>276</v>
+      </c>
+      <c r="E69">
+        <v>2023</v>
+      </c>
+      <c r="F69" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>136</v>
       </c>
@@ -2402,14 +2660,17 @@
       <c r="C70" t="s">
         <v>254</v>
       </c>
-      <c r="D70">
-        <v>2023</v>
-      </c>
-      <c r="E70" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D70" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70">
+        <v>2023</v>
+      </c>
+      <c r="F70" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>138</v>
       </c>
@@ -2419,14 +2680,17 @@
       <c r="C71" t="s">
         <v>254</v>
       </c>
-      <c r="D71">
-        <v>2023</v>
-      </c>
-      <c r="E71" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D71" t="s">
+        <v>276</v>
+      </c>
+      <c r="E71">
+        <v>2023</v>
+      </c>
+      <c r="F71" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>140</v>
       </c>
@@ -2436,14 +2700,17 @@
       <c r="C72" t="s">
         <v>254</v>
       </c>
-      <c r="D72">
-        <v>2023</v>
-      </c>
-      <c r="E72" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D72" t="s">
+        <v>276</v>
+      </c>
+      <c r="E72">
+        <v>2023</v>
+      </c>
+      <c r="F72" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -2453,14 +2720,17 @@
       <c r="C73" t="s">
         <v>254</v>
       </c>
-      <c r="D73">
-        <v>2023</v>
-      </c>
-      <c r="E73" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D73" t="s">
+        <v>276</v>
+      </c>
+      <c r="E73">
+        <v>2023</v>
+      </c>
+      <c r="F73" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>144</v>
       </c>
@@ -2470,14 +2740,17 @@
       <c r="C74" t="s">
         <v>254</v>
       </c>
-      <c r="D74">
-        <v>2023</v>
-      </c>
-      <c r="E74" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D74" t="s">
+        <v>276</v>
+      </c>
+      <c r="E74">
+        <v>2023</v>
+      </c>
+      <c r="F74" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>146</v>
       </c>
@@ -2487,14 +2760,17 @@
       <c r="C75" t="s">
         <v>254</v>
       </c>
-      <c r="D75">
-        <v>2023</v>
-      </c>
-      <c r="E75" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D75" t="s">
+        <v>276</v>
+      </c>
+      <c r="E75">
+        <v>2023</v>
+      </c>
+      <c r="F75" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>148</v>
       </c>
@@ -2504,14 +2780,17 @@
       <c r="C76" t="s">
         <v>254</v>
       </c>
-      <c r="D76">
-        <v>2023</v>
-      </c>
-      <c r="E76" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D76" t="s">
+        <v>276</v>
+      </c>
+      <c r="E76">
+        <v>2023</v>
+      </c>
+      <c r="F76" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>150</v>
       </c>
@@ -2521,14 +2800,17 @@
       <c r="C77" t="s">
         <v>254</v>
       </c>
-      <c r="D77">
-        <v>2023</v>
-      </c>
-      <c r="E77" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D77" t="s">
+        <v>276</v>
+      </c>
+      <c r="E77">
+        <v>2023</v>
+      </c>
+      <c r="F77" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>152</v>
       </c>
@@ -2538,14 +2820,17 @@
       <c r="C78" t="s">
         <v>254</v>
       </c>
-      <c r="D78">
-        <v>2023</v>
-      </c>
-      <c r="E78" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D78" t="s">
+        <v>276</v>
+      </c>
+      <c r="E78">
+        <v>2023</v>
+      </c>
+      <c r="F78" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -2555,14 +2840,17 @@
       <c r="C79" t="s">
         <v>253</v>
       </c>
-      <c r="D79">
-        <v>2023</v>
-      </c>
-      <c r="E79" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D79" t="s">
+        <v>277</v>
+      </c>
+      <c r="E79">
+        <v>2023</v>
+      </c>
+      <c r="F79" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>156</v>
       </c>
@@ -2572,14 +2860,17 @@
       <c r="C80" t="s">
         <v>253</v>
       </c>
-      <c r="D80">
-        <v>2023</v>
-      </c>
-      <c r="E80" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D80" t="s">
+        <v>277</v>
+      </c>
+      <c r="E80">
+        <v>2023</v>
+      </c>
+      <c r="F80" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>158</v>
       </c>
@@ -2589,14 +2880,17 @@
       <c r="C81" t="s">
         <v>253</v>
       </c>
-      <c r="D81">
-        <v>2023</v>
-      </c>
-      <c r="E81" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D81" t="s">
+        <v>277</v>
+      </c>
+      <c r="E81">
+        <v>2023</v>
+      </c>
+      <c r="F81" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>160</v>
       </c>
@@ -2606,14 +2900,17 @@
       <c r="C82" t="s">
         <v>255</v>
       </c>
-      <c r="D82">
-        <v>2023</v>
-      </c>
-      <c r="E82" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D82" t="s">
+        <v>278</v>
+      </c>
+      <c r="E82">
+        <v>2023</v>
+      </c>
+      <c r="F82" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>162</v>
       </c>
@@ -2623,14 +2920,17 @@
       <c r="C83" t="s">
         <v>253</v>
       </c>
-      <c r="D83">
-        <v>2023</v>
-      </c>
-      <c r="E83" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D83" t="s">
+        <v>279</v>
+      </c>
+      <c r="E83">
+        <v>2023</v>
+      </c>
+      <c r="F83" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>164</v>
       </c>
@@ -2640,14 +2940,17 @@
       <c r="C84" t="s">
         <v>253</v>
       </c>
-      <c r="D84">
-        <v>2023</v>
-      </c>
-      <c r="E84" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D84" t="s">
+        <v>279</v>
+      </c>
+      <c r="E84">
+        <v>2023</v>
+      </c>
+      <c r="F84" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -2657,14 +2960,17 @@
       <c r="C85" t="s">
         <v>253</v>
       </c>
-      <c r="D85">
-        <v>2023</v>
-      </c>
-      <c r="E85" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D85" t="s">
+        <v>279</v>
+      </c>
+      <c r="E85">
+        <v>2023</v>
+      </c>
+      <c r="F85" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>168</v>
       </c>
@@ -2674,14 +2980,17 @@
       <c r="C86" t="s">
         <v>253</v>
       </c>
-      <c r="D86">
-        <v>2023</v>
-      </c>
-      <c r="E86" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D86" t="s">
+        <v>279</v>
+      </c>
+      <c r="E86">
+        <v>2023</v>
+      </c>
+      <c r="F86" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>170</v>
       </c>
@@ -2691,14 +3000,17 @@
       <c r="C87" t="s">
         <v>256</v>
       </c>
-      <c r="D87">
-        <v>2023</v>
-      </c>
-      <c r="E87" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D87" t="s">
+        <v>280</v>
+      </c>
+      <c r="E87">
+        <v>2023</v>
+      </c>
+      <c r="F87" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>172</v>
       </c>
@@ -2708,14 +3020,17 @@
       <c r="C88" t="s">
         <v>256</v>
       </c>
-      <c r="D88">
-        <v>2023</v>
-      </c>
-      <c r="E88" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D88" t="s">
+        <v>280</v>
+      </c>
+      <c r="E88">
+        <v>2023</v>
+      </c>
+      <c r="F88" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>174</v>
       </c>
@@ -2725,14 +3040,17 @@
       <c r="C89" t="s">
         <v>256</v>
       </c>
-      <c r="D89">
-        <v>2023</v>
-      </c>
-      <c r="E89" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D89" t="s">
+        <v>280</v>
+      </c>
+      <c r="E89">
+        <v>2023</v>
+      </c>
+      <c r="F89" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>176</v>
       </c>
@@ -2742,14 +3060,17 @@
       <c r="C90" t="s">
         <v>256</v>
       </c>
-      <c r="D90">
-        <v>2023</v>
-      </c>
-      <c r="E90" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D90" t="s">
+        <v>280</v>
+      </c>
+      <c r="E90">
+        <v>2023</v>
+      </c>
+      <c r="F90" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>178</v>
       </c>
@@ -2759,14 +3080,17 @@
       <c r="C91" t="s">
         <v>256</v>
       </c>
-      <c r="D91">
-        <v>2023</v>
-      </c>
-      <c r="E91" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D91" t="s">
+        <v>280</v>
+      </c>
+      <c r="E91">
+        <v>2023</v>
+      </c>
+      <c r="F91" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>180</v>
       </c>
@@ -2776,14 +3100,17 @@
       <c r="C92" t="s">
         <v>256</v>
       </c>
-      <c r="D92">
-        <v>2023</v>
-      </c>
-      <c r="E92" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D92" t="s">
+        <v>280</v>
+      </c>
+      <c r="E92">
+        <v>2023</v>
+      </c>
+      <c r="F92" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>182</v>
       </c>
@@ -2793,14 +3120,17 @@
       <c r="C93" t="s">
         <v>256</v>
       </c>
-      <c r="D93">
-        <v>2023</v>
-      </c>
-      <c r="E93" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D93" t="s">
+        <v>280</v>
+      </c>
+      <c r="E93">
+        <v>2023</v>
+      </c>
+      <c r="F93" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>184</v>
       </c>
@@ -2810,14 +3140,17 @@
       <c r="C94" t="s">
         <v>256</v>
       </c>
-      <c r="D94">
-        <v>2023</v>
-      </c>
-      <c r="E94" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D94" t="s">
+        <v>280</v>
+      </c>
+      <c r="E94">
+        <v>2023</v>
+      </c>
+      <c r="F94" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>186</v>
       </c>
@@ -2827,14 +3160,17 @@
       <c r="C95" t="s">
         <v>256</v>
       </c>
-      <c r="D95">
-        <v>2023</v>
-      </c>
-      <c r="E95" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D95" t="s">
+        <v>280</v>
+      </c>
+      <c r="E95">
+        <v>2023</v>
+      </c>
+      <c r="F95" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>188</v>
       </c>
@@ -2844,14 +3180,17 @@
       <c r="C96" t="s">
         <v>256</v>
       </c>
-      <c r="D96">
-        <v>2023</v>
-      </c>
-      <c r="E96" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D96" t="s">
+        <v>280</v>
+      </c>
+      <c r="E96">
+        <v>2023</v>
+      </c>
+      <c r="F96" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>190</v>
       </c>
@@ -2861,14 +3200,17 @@
       <c r="C97" t="s">
         <v>256</v>
       </c>
-      <c r="D97">
-        <v>2023</v>
-      </c>
-      <c r="E97" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D97" t="s">
+        <v>280</v>
+      </c>
+      <c r="E97">
+        <v>2023</v>
+      </c>
+      <c r="F97" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -2878,777 +3220,945 @@
       <c r="C98" t="s">
         <v>254</v>
       </c>
-      <c r="D98">
-        <v>2023</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="D98" t="s">
+        <v>281</v>
+      </c>
+      <c r="E98">
+        <v>2023</v>
+      </c>
+      <c r="F98" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>194</v>
       </c>
       <c r="B99" t="s">
         <v>252</v>
       </c>
-      <c r="E99" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D99" t="s">
+        <v>282</v>
+      </c>
+      <c r="F99" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
         <v>195</v>
       </c>
       <c r="C100" t="s">
         <v>257</v>
       </c>
-      <c r="D100">
+      <c r="D100" t="s">
+        <v>282</v>
+      </c>
+      <c r="E100">
         <v>2013</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
         <v>196</v>
       </c>
       <c r="C101" t="s">
         <v>258</v>
       </c>
-      <c r="D101">
+      <c r="D101" t="s">
+        <v>282</v>
+      </c>
+      <c r="E101">
         <v>2008</v>
       </c>
-      <c r="E101" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F101" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
         <v>197</v>
       </c>
       <c r="C102" t="s">
         <v>258</v>
       </c>
-      <c r="D102">
+      <c r="D102" t="s">
+        <v>282</v>
+      </c>
+      <c r="E102">
         <v>2008</v>
       </c>
-      <c r="E102" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F102" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
         <v>198</v>
       </c>
       <c r="C103" t="s">
         <v>258</v>
       </c>
-      <c r="D103">
+      <c r="D103" t="s">
+        <v>282</v>
+      </c>
+      <c r="E103">
         <v>2008</v>
       </c>
-      <c r="E103" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F103" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
         <v>199</v>
       </c>
       <c r="C104" t="s">
         <v>258</v>
       </c>
-      <c r="D104">
+      <c r="D104" t="s">
+        <v>282</v>
+      </c>
+      <c r="E104">
         <v>2008</v>
       </c>
-      <c r="E104" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F104" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
         <v>200</v>
       </c>
       <c r="C105" t="s">
         <v>258</v>
       </c>
-      <c r="D105">
+      <c r="D105" t="s">
+        <v>282</v>
+      </c>
+      <c r="E105">
         <v>2008</v>
       </c>
-      <c r="E105" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F105" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
         <v>201</v>
       </c>
       <c r="C106" t="s">
         <v>258</v>
       </c>
-      <c r="D106">
+      <c r="D106" t="s">
+        <v>282</v>
+      </c>
+      <c r="E106">
         <v>2008</v>
       </c>
-      <c r="E106" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F106" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
         <v>202</v>
       </c>
       <c r="C107" t="s">
         <v>253</v>
       </c>
-      <c r="D107">
+      <c r="D107" t="s">
+        <v>282</v>
+      </c>
+      <c r="E107">
         <v>2017</v>
       </c>
-      <c r="E107" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F107" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
         <v>203</v>
       </c>
       <c r="C108" t="s">
         <v>253</v>
       </c>
-      <c r="D108">
+      <c r="D108" t="s">
+        <v>282</v>
+      </c>
+      <c r="E108">
         <v>2018</v>
       </c>
-      <c r="E108" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F108" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
         <v>204</v>
       </c>
       <c r="C109" t="s">
         <v>258</v>
       </c>
-      <c r="D109">
+      <c r="D109" t="s">
+        <v>282</v>
+      </c>
+      <c r="E109">
         <v>2018</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
         <v>205</v>
       </c>
       <c r="C110" t="s">
         <v>258</v>
       </c>
-      <c r="D110">
+      <c r="D110" t="s">
+        <v>282</v>
+      </c>
+      <c r="E110">
         <v>2018</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
         <v>206</v>
       </c>
       <c r="C111" t="s">
         <v>258</v>
       </c>
-      <c r="D111">
+      <c r="D111" t="s">
+        <v>282</v>
+      </c>
+      <c r="E111">
         <v>2018</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
         <v>207</v>
       </c>
       <c r="C112" t="s">
         <v>258</v>
       </c>
-      <c r="D112">
+      <c r="D112" t="s">
+        <v>282</v>
+      </c>
+      <c r="E112">
         <v>2018</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
         <v>208</v>
       </c>
       <c r="C113" t="s">
         <v>258</v>
       </c>
-      <c r="D113">
+      <c r="D113" t="s">
+        <v>282</v>
+      </c>
+      <c r="E113">
         <v>2018</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
         <v>209</v>
       </c>
       <c r="C114" t="s">
         <v>258</v>
       </c>
-      <c r="D114">
+      <c r="D114" t="s">
+        <v>282</v>
+      </c>
+      <c r="E114">
         <v>2018</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
         <v>210</v>
       </c>
       <c r="C115" t="s">
         <v>258</v>
       </c>
-      <c r="D115">
+      <c r="D115" t="s">
+        <v>282</v>
+      </c>
+      <c r="E115">
         <v>2018</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
         <v>211</v>
       </c>
       <c r="C116" t="s">
         <v>258</v>
       </c>
-      <c r="D116">
+      <c r="D116" t="s">
+        <v>282</v>
+      </c>
+      <c r="E116">
         <v>2018</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
         <v>212</v>
       </c>
       <c r="C117" t="s">
         <v>258</v>
       </c>
-      <c r="D117">
+      <c r="D117" t="s">
+        <v>282</v>
+      </c>
+      <c r="E117">
         <v>2018</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
         <v>213</v>
       </c>
       <c r="C118" t="s">
         <v>258</v>
       </c>
-      <c r="D118">
+      <c r="D118" t="s">
+        <v>282</v>
+      </c>
+      <c r="E118">
         <v>2018</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
         <v>214</v>
       </c>
       <c r="C119" t="s">
         <v>258</v>
       </c>
-      <c r="D119">
+      <c r="D119" t="s">
+        <v>282</v>
+      </c>
+      <c r="E119">
         <v>2018</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
         <v>215</v>
       </c>
       <c r="C120" t="s">
         <v>258</v>
       </c>
-      <c r="D120">
+      <c r="D120" t="s">
+        <v>282</v>
+      </c>
+      <c r="E120">
         <v>2018</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
         <v>216</v>
       </c>
       <c r="C121" t="s">
         <v>258</v>
       </c>
-      <c r="D121">
+      <c r="D121" t="s">
+        <v>282</v>
+      </c>
+      <c r="E121">
         <v>2018</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
         <v>217</v>
       </c>
       <c r="C122" t="s">
         <v>258</v>
       </c>
-      <c r="D122">
+      <c r="D122" t="s">
+        <v>282</v>
+      </c>
+      <c r="E122">
         <v>2018</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
         <v>218</v>
       </c>
       <c r="C123" t="s">
         <v>253</v>
       </c>
-      <c r="D123">
+      <c r="D123" t="s">
+        <v>282</v>
+      </c>
+      <c r="E123">
         <v>2020</v>
       </c>
-      <c r="E123" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F123" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
         <v>219</v>
       </c>
       <c r="C124" t="s">
         <v>253</v>
       </c>
-      <c r="D124">
+      <c r="D124" t="s">
+        <v>282</v>
+      </c>
+      <c r="E124">
         <v>2020</v>
       </c>
-      <c r="E124" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F124" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
         <v>220</v>
       </c>
       <c r="C125" t="s">
         <v>253</v>
       </c>
-      <c r="D125">
+      <c r="D125" t="s">
+        <v>282</v>
+      </c>
+      <c r="E125">
         <v>2020</v>
       </c>
-      <c r="E125" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F125" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
         <v>221</v>
       </c>
       <c r="C126" t="s">
         <v>253</v>
       </c>
-      <c r="D126">
+      <c r="D126" t="s">
+        <v>282</v>
+      </c>
+      <c r="E126">
         <v>2020</v>
       </c>
-      <c r="E126" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F126" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
         <v>222</v>
       </c>
       <c r="C127" t="s">
         <v>253</v>
       </c>
-      <c r="D127">
+      <c r="D127" t="s">
+        <v>282</v>
+      </c>
+      <c r="E127">
         <v>2020</v>
       </c>
-      <c r="E127" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F127" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
         <v>223</v>
       </c>
       <c r="C128" t="s">
         <v>253</v>
       </c>
-      <c r="D128">
+      <c r="D128" t="s">
+        <v>282</v>
+      </c>
+      <c r="E128">
         <v>2020</v>
       </c>
-      <c r="E128" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F128" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B129" t="s">
         <v>224</v>
       </c>
       <c r="C129" t="s">
         <v>253</v>
       </c>
-      <c r="D129">
+      <c r="D129" t="s">
+        <v>282</v>
+      </c>
+      <c r="E129">
         <v>2021</v>
       </c>
-      <c r="E129" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F129" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
         <v>225</v>
       </c>
       <c r="C130" t="s">
         <v>253</v>
       </c>
-      <c r="D130">
+      <c r="D130" t="s">
+        <v>282</v>
+      </c>
+      <c r="E130">
         <v>2021</v>
       </c>
-      <c r="E130" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F130" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
         <v>226</v>
       </c>
       <c r="C131" t="s">
         <v>253</v>
       </c>
-      <c r="D131">
+      <c r="D131" t="s">
+        <v>282</v>
+      </c>
+      <c r="E131">
         <v>2021</v>
       </c>
-      <c r="E131" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F131" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
         <v>227</v>
       </c>
       <c r="C132" t="s">
         <v>253</v>
       </c>
-      <c r="D132">
+      <c r="D132" t="s">
+        <v>282</v>
+      </c>
+      <c r="E132">
         <v>2021</v>
       </c>
-      <c r="E132" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F132" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
         <v>228</v>
       </c>
       <c r="C133" t="s">
         <v>253</v>
       </c>
-      <c r="D133">
+      <c r="D133" t="s">
+        <v>282</v>
+      </c>
+      <c r="E133">
         <v>2021</v>
       </c>
-      <c r="E133" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F133" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
         <v>229</v>
       </c>
       <c r="C134" t="s">
         <v>253</v>
       </c>
-      <c r="D134">
+      <c r="D134" t="s">
+        <v>282</v>
+      </c>
+      <c r="E134">
         <v>2021</v>
       </c>
-      <c r="E134" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F134" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B135" t="s">
         <v>230</v>
       </c>
       <c r="C135" t="s">
         <v>253</v>
       </c>
-      <c r="D135">
+      <c r="D135" t="s">
+        <v>282</v>
+      </c>
+      <c r="E135">
         <v>2021</v>
       </c>
-      <c r="E135" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F135" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B136" t="s">
         <v>231</v>
       </c>
       <c r="C136" t="s">
         <v>253</v>
       </c>
-      <c r="D136">
+      <c r="D136" t="s">
+        <v>282</v>
+      </c>
+      <c r="E136">
         <v>2021</v>
       </c>
-      <c r="E136" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F136" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B137" t="s">
         <v>232</v>
       </c>
       <c r="C137" t="s">
         <v>253</v>
       </c>
-      <c r="D137">
+      <c r="D137" t="s">
+        <v>282</v>
+      </c>
+      <c r="E137">
         <v>2021</v>
       </c>
-      <c r="E137" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F137" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B138" t="s">
         <v>233</v>
       </c>
       <c r="C138" t="s">
         <v>253</v>
       </c>
-      <c r="D138">
+      <c r="D138" t="s">
+        <v>282</v>
+      </c>
+      <c r="E138">
         <v>2021</v>
       </c>
-      <c r="E138" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F138" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B139" t="s">
         <v>234</v>
       </c>
       <c r="C139" t="s">
         <v>253</v>
       </c>
-      <c r="D139">
+      <c r="D139" t="s">
+        <v>282</v>
+      </c>
+      <c r="E139">
         <v>2021</v>
       </c>
-      <c r="E139" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F139" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
         <v>235</v>
       </c>
       <c r="C140" t="s">
         <v>253</v>
       </c>
-      <c r="D140">
+      <c r="D140" t="s">
+        <v>282</v>
+      </c>
+      <c r="E140">
         <v>2021</v>
       </c>
-      <c r="E140" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F140" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="141" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
         <v>236</v>
       </c>
       <c r="C141" t="s">
         <v>253</v>
       </c>
-      <c r="D141">
+      <c r="D141" t="s">
+        <v>282</v>
+      </c>
+      <c r="E141">
         <v>2021</v>
       </c>
-      <c r="E141" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F141" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
         <v>237</v>
       </c>
       <c r="C142" t="s">
         <v>253</v>
       </c>
-      <c r="D142">
+      <c r="D142" t="s">
+        <v>282</v>
+      </c>
+      <c r="E142">
         <v>2021</v>
       </c>
-      <c r="E142" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F142" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
         <v>238</v>
       </c>
       <c r="C143" t="s">
         <v>253</v>
       </c>
-      <c r="D143">
+      <c r="D143" t="s">
+        <v>282</v>
+      </c>
+      <c r="E143">
         <v>2021</v>
       </c>
-      <c r="E143" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F143" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B144" t="s">
         <v>239</v>
       </c>
       <c r="C144" t="s">
         <v>253</v>
       </c>
-      <c r="D144">
+      <c r="D144" t="s">
+        <v>282</v>
+      </c>
+      <c r="E144">
         <v>2021</v>
       </c>
-      <c r="E144" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F144" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B145" t="s">
         <v>240</v>
       </c>
       <c r="C145" t="s">
         <v>253</v>
       </c>
-      <c r="D145">
+      <c r="D145" t="s">
+        <v>282</v>
+      </c>
+      <c r="E145">
         <v>2021</v>
       </c>
-      <c r="E145" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F145" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B146" t="s">
         <v>241</v>
       </c>
       <c r="C146" t="s">
         <v>253</v>
       </c>
-      <c r="D146">
+      <c r="D146" t="s">
+        <v>282</v>
+      </c>
+      <c r="E146">
         <v>2021</v>
       </c>
-      <c r="E146" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F146" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B147" t="s">
         <v>242</v>
       </c>
       <c r="C147" t="s">
         <v>253</v>
       </c>
-      <c r="D147">
+      <c r="D147" t="s">
+        <v>282</v>
+      </c>
+      <c r="E147">
         <v>2021</v>
       </c>
-      <c r="E147" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F147" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B148" t="s">
         <v>243</v>
       </c>
       <c r="C148" t="s">
         <v>259</v>
       </c>
-      <c r="D148">
+      <c r="D148" t="s">
+        <v>282</v>
+      </c>
+      <c r="E148">
         <v>1908</v>
       </c>
-      <c r="E148" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F148" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
         <v>244</v>
       </c>
       <c r="C149" t="s">
         <v>259</v>
       </c>
-      <c r="D149">
+      <c r="D149" t="s">
+        <v>282</v>
+      </c>
+      <c r="E149">
         <v>1930</v>
       </c>
-      <c r="E149" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F149" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B150" t="s">
         <v>245</v>
       </c>
       <c r="C150" t="s">
         <v>260</v>
       </c>
-      <c r="D150">
+      <c r="D150" t="s">
+        <v>282</v>
+      </c>
+      <c r="E150">
         <v>1919</v>
       </c>
-      <c r="E150" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F150" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B151" t="s">
         <v>246</v>
       </c>
       <c r="C151" t="s">
         <v>256</v>
       </c>
-      <c r="D151">
+      <c r="D151" t="s">
+        <v>282</v>
+      </c>
+      <c r="E151">
         <v>1963</v>
       </c>
-      <c r="E151" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="F151" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B152" t="s">
         <v>247</v>
       </c>
       <c r="C152" t="s">
         <v>261</v>
       </c>
-      <c r="D152">
+      <c r="D152" t="s">
+        <v>282</v>
+      </c>
+      <c r="E152">
         <v>2000</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B153" t="s">
         <v>248</v>
       </c>
       <c r="C153" t="s">
         <v>261</v>
       </c>
-      <c r="D153">
+      <c r="D153" t="s">
+        <v>282</v>
+      </c>
+      <c r="E153">
         <v>2011</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>267</v>
       </c>
     </row>

--- a/analyses/trees/RNA1/RNA1_Seq_IDs.xlsx
+++ b/analyses/trees/RNA1/RNA1_Seq_IDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lexikeene/Documents/Research/diverse_collections/github/analyses/trees/RNA1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5FE7A4-D92B-724D-A1F9-272A3581F143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E110BC-2D33-C148-987E-F042B30D8B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32400" yWindow="500" windowWidth="17240" windowHeight="21100" xr2:uid="{C5CC4E02-00F2-344F-A047-B9E9E3AD013B}"/>
+    <workbookView xWindow="32400" yWindow="500" windowWidth="33580" windowHeight="21100" xr2:uid="{C5CC4E02-00F2-344F-A047-B9E9E3AD013B}"/>
   </bookViews>
   <sheets>
     <sheet name="RNA1_Seq_IDs" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="381">
   <si>
     <t>D_mel_USA_2020_mel-20-TD-3_Galbut_virus_RNA1_Complete_CDS</t>
   </si>
@@ -891,6 +891,294 @@
   </si>
   <si>
     <t>Michener</t>
+  </si>
+  <si>
+    <t>sample_id</t>
+  </si>
+  <si>
+    <t>mel-20-TD-3</t>
+  </si>
+  <si>
+    <t>sim-20-TD-4</t>
+  </si>
+  <si>
+    <t>mel-21-MDS-9</t>
+  </si>
+  <si>
+    <t>500-F-11</t>
+  </si>
+  <si>
+    <t>500-F-21</t>
+  </si>
+  <si>
+    <t>500-F-41</t>
+  </si>
+  <si>
+    <t>500-F-67</t>
+  </si>
+  <si>
+    <t>500-M-16</t>
+  </si>
+  <si>
+    <t>500-M-17</t>
+  </si>
+  <si>
+    <t>500-M-54</t>
+  </si>
+  <si>
+    <t>500-M-57</t>
+  </si>
+  <si>
+    <t>500-M-60</t>
+  </si>
+  <si>
+    <t>500-M-61-2</t>
+  </si>
+  <si>
+    <t>500-M-61</t>
+  </si>
+  <si>
+    <t>500-M-65-2</t>
+  </si>
+  <si>
+    <t>500-M-65</t>
+  </si>
+  <si>
+    <t>500-M-71-2</t>
+  </si>
+  <si>
+    <t>500-M-83</t>
+  </si>
+  <si>
+    <t>500-M-84</t>
+  </si>
+  <si>
+    <t>500-M-F10</t>
+  </si>
+  <si>
+    <t>500-M-F11</t>
+  </si>
+  <si>
+    <t>500-M-G2</t>
+  </si>
+  <si>
+    <t>1020-A7</t>
+  </si>
+  <si>
+    <t>1020-B6</t>
+  </si>
+  <si>
+    <t>1020-C2</t>
+  </si>
+  <si>
+    <t>1020-D1</t>
+  </si>
+  <si>
+    <t>1020-D3</t>
+  </si>
+  <si>
+    <t>1020-F1</t>
+  </si>
+  <si>
+    <t>1020-F6</t>
+  </si>
+  <si>
+    <t>1020-F-31</t>
+  </si>
+  <si>
+    <t>1020-F-36</t>
+  </si>
+  <si>
+    <t>1020-F-40</t>
+  </si>
+  <si>
+    <t>1020-F-44</t>
+  </si>
+  <si>
+    <t>1020-F-0818-D4</t>
+  </si>
+  <si>
+    <t>1020-F-0818-D11</t>
+  </si>
+  <si>
+    <t>1020-G3</t>
+  </si>
+  <si>
+    <t>1020-M-8</t>
+  </si>
+  <si>
+    <t>1020-M-19</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A5</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A7</t>
+  </si>
+  <si>
+    <t>1020-M-0818-A10</t>
+  </si>
+  <si>
+    <t>1428-F-8</t>
+  </si>
+  <si>
+    <t>1428-F-21</t>
+  </si>
+  <si>
+    <t>1428-M-3</t>
+  </si>
+  <si>
+    <t>1428-M-4</t>
+  </si>
+  <si>
+    <t>1428-M-21</t>
+  </si>
+  <si>
+    <t>1428-M-42</t>
+  </si>
+  <si>
+    <t>Adobe-B4</t>
+  </si>
+  <si>
+    <t>Adobe-B6</t>
+  </si>
+  <si>
+    <t>Adobe-B8</t>
+  </si>
+  <si>
+    <t>Adobe-C2</t>
+  </si>
+  <si>
+    <t>Briarwood-D9</t>
+  </si>
+  <si>
+    <t>CVID-0825-B1</t>
+  </si>
+  <si>
+    <t>CVID-0825-C10</t>
+  </si>
+  <si>
+    <t>CVID-0911-F4</t>
+  </si>
+  <si>
+    <t>CVID-1006-G6</t>
+  </si>
+  <si>
+    <t>CVID-1006-G7</t>
+  </si>
+  <si>
+    <t>CVID-1006-H2</t>
+  </si>
+  <si>
+    <t>CVID-1006-H3</t>
+  </si>
+  <si>
+    <t>James-A4</t>
+  </si>
+  <si>
+    <t>James-A5</t>
+  </si>
+  <si>
+    <t>ME-F-1</t>
+  </si>
+  <si>
+    <t>ME-F-3</t>
+  </si>
+  <si>
+    <t>ME-M-1</t>
+  </si>
+  <si>
+    <t>ME-M-2</t>
+  </si>
+  <si>
+    <t>ME-M-4</t>
+  </si>
+  <si>
+    <t>ME-M-6</t>
+  </si>
+  <si>
+    <t>ME-M-8</t>
+  </si>
+  <si>
+    <t>ME-M-10</t>
+  </si>
+  <si>
+    <t>ME-M-11</t>
+  </si>
+  <si>
+    <t>ME-M-14</t>
+  </si>
+  <si>
+    <t>ME-M-17</t>
+  </si>
+  <si>
+    <t>ME-M-18</t>
+  </si>
+  <si>
+    <t>ME-M-19</t>
+  </si>
+  <si>
+    <t>ME-M-20</t>
+  </si>
+  <si>
+    <t>Myrtle-D5</t>
+  </si>
+  <si>
+    <t>Myrtle-D11</t>
+  </si>
+  <si>
+    <t>Myrtle-E9</t>
+  </si>
+  <si>
+    <t>OH-M-5</t>
+  </si>
+  <si>
+    <t>Peach-8-F7</t>
+  </si>
+  <si>
+    <t>Peach-9-F8</t>
+  </si>
+  <si>
+    <t>Peach-10-F10</t>
+  </si>
+  <si>
+    <t>Peach-13-H7</t>
+  </si>
+  <si>
+    <t>Penn-F-2</t>
+  </si>
+  <si>
+    <t>Penn-F-3</t>
+  </si>
+  <si>
+    <t>Penn-F-9</t>
+  </si>
+  <si>
+    <t>Penn-F-12</t>
+  </si>
+  <si>
+    <t>Penn-M-2</t>
+  </si>
+  <si>
+    <t>Penn-M-8</t>
+  </si>
+  <si>
+    <t>Penn-M-10</t>
+  </si>
+  <si>
+    <t>Penn-M-14</t>
+  </si>
+  <si>
+    <t>Penn-M-15</t>
+  </si>
+  <si>
+    <t>ME-M-3</t>
+  </si>
+  <si>
+    <t>Penn-F-4</t>
+  </si>
+  <si>
+    <t>ME-M-7</t>
   </si>
 </sst>
 </file>
@@ -1262,15 +1550,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{395C2393-5C50-2A47-93A3-2BB7B4877225}">
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>251</v>
       </c>
@@ -1289,8 +1578,11 @@
       <c r="F1" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1309,8 +1601,11 @@
       <c r="F2" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1329,8 +1624,11 @@
       <c r="F3" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1349,8 +1647,11 @@
       <c r="F4" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1369,8 +1670,11 @@
       <c r="F5" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1389,8 +1693,11 @@
       <c r="F6" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1409,8 +1716,11 @@
       <c r="F7" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1429,8 +1739,11 @@
       <c r="F8" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1449,8 +1762,11 @@
       <c r="F9" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1469,8 +1785,11 @@
       <c r="F10" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1489,8 +1808,11 @@
       <c r="F11" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1509,8 +1831,11 @@
       <c r="F12" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1529,8 +1854,11 @@
       <c r="F13" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1877,11 @@
       <c r="F14" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1569,8 +1900,11 @@
       <c r="F15" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1589,8 +1923,11 @@
       <c r="F16" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -1609,8 +1946,11 @@
       <c r="F17" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G17" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1969,11 @@
       <c r="F18" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1649,8 +1992,11 @@
       <c r="F19" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1669,8 +2015,11 @@
       <c r="F20" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1689,8 +2038,11 @@
       <c r="F21" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G21" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1709,8 +2061,11 @@
       <c r="F22" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -1729,8 +2084,11 @@
       <c r="F23" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -1749,8 +2107,11 @@
       <c r="F24" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G24" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -1769,8 +2130,11 @@
       <c r="F25" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -1789,8 +2153,11 @@
       <c r="F26" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G26" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>50</v>
       </c>
@@ -1809,8 +2176,11 @@
       <c r="F27" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G27" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1829,8 +2199,11 @@
       <c r="F28" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G28" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -1849,8 +2222,11 @@
       <c r="F29" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G29" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -1869,8 +2245,11 @@
       <c r="F30" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G30" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>58</v>
       </c>
@@ -1889,8 +2268,11 @@
       <c r="F31" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G31" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -1909,8 +2291,11 @@
       <c r="F32" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G32" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>62</v>
       </c>
@@ -1929,8 +2314,11 @@
       <c r="F33" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G33" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -1949,8 +2337,11 @@
       <c r="F34" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G34" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -1969,8 +2360,11 @@
       <c r="F35" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G35" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1989,8 +2383,11 @@
       <c r="F36" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G36" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -2009,8 +2406,11 @@
       <c r="F37" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G37" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -2029,8 +2429,11 @@
       <c r="F38" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G38" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2049,8 +2452,11 @@
       <c r="F39" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G39" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -2069,8 +2475,11 @@
       <c r="F40" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G40" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>78</v>
       </c>
@@ -2089,8 +2498,11 @@
       <c r="F41" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G41" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -2109,8 +2521,11 @@
       <c r="F42" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G42" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -2129,8 +2544,11 @@
       <c r="F43" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G43" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>84</v>
       </c>
@@ -2149,8 +2567,11 @@
       <c r="F44" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G44" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -2169,8 +2590,11 @@
       <c r="F45" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G45" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>88</v>
       </c>
@@ -2189,8 +2613,11 @@
       <c r="F46" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G46" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>90</v>
       </c>
@@ -2209,8 +2636,11 @@
       <c r="F47" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G47" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -2229,8 +2659,11 @@
       <c r="F48" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G48" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>94</v>
       </c>
@@ -2249,8 +2682,11 @@
       <c r="F49" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G49" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -2269,8 +2705,11 @@
       <c r="F50" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G50" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>98</v>
       </c>
@@ -2289,8 +2728,11 @@
       <c r="F51" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G51" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>100</v>
       </c>
@@ -2309,8 +2751,11 @@
       <c r="F52" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G52" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>102</v>
       </c>
@@ -2329,8 +2774,11 @@
       <c r="F53" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G53" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -2349,8 +2797,11 @@
       <c r="F54" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G54" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>106</v>
       </c>
@@ -2369,8 +2820,11 @@
       <c r="F55" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G55" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -2389,8 +2843,11 @@
       <c r="F56" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G56" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -2409,8 +2866,11 @@
       <c r="F57" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G57" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -2429,8 +2889,11 @@
       <c r="F58" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G58" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>114</v>
       </c>
@@ -2449,8 +2912,11 @@
       <c r="F59" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G59" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -2469,8 +2935,11 @@
       <c r="F60" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>118</v>
       </c>
@@ -2489,8 +2958,11 @@
       <c r="F61" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G61" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>120</v>
       </c>
@@ -2509,8 +2981,11 @@
       <c r="F62" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G62" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>122</v>
       </c>
@@ -2529,8 +3004,11 @@
       <c r="F63" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G63" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>124</v>
       </c>
@@ -2549,8 +3027,11 @@
       <c r="F64" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G64" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>126</v>
       </c>
@@ -2569,8 +3050,11 @@
       <c r="F65" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G65" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>128</v>
       </c>
@@ -2589,8 +3073,11 @@
       <c r="F66" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G66" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>130</v>
       </c>
@@ -2609,8 +3096,11 @@
       <c r="F67" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G67" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>132</v>
       </c>
@@ -2629,8 +3119,11 @@
       <c r="F68" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G68" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>134</v>
       </c>
@@ -2649,8 +3142,11 @@
       <c r="F69" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G69" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>136</v>
       </c>
@@ -2669,8 +3165,11 @@
       <c r="F70" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G70" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>138</v>
       </c>
@@ -2689,8 +3188,11 @@
       <c r="F71" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G71" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>140</v>
       </c>
@@ -2709,8 +3211,11 @@
       <c r="F72" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G72" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -2729,8 +3234,11 @@
       <c r="F73" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G73" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>144</v>
       </c>
@@ -2749,8 +3257,11 @@
       <c r="F74" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G74" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>146</v>
       </c>
@@ -2769,8 +3280,11 @@
       <c r="F75" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G75" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>148</v>
       </c>
@@ -2789,8 +3303,11 @@
       <c r="F76" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G76" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>150</v>
       </c>
@@ -2809,8 +3326,11 @@
       <c r="F77" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G77" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>152</v>
       </c>
@@ -2829,8 +3349,11 @@
       <c r="F78" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G78" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -2849,8 +3372,11 @@
       <c r="F79" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G79" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>156</v>
       </c>
@@ -2869,8 +3395,11 @@
       <c r="F80" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G80" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>158</v>
       </c>
@@ -2889,8 +3418,11 @@
       <c r="F81" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G81" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>160</v>
       </c>
@@ -2909,8 +3441,11 @@
       <c r="F82" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G82" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>162</v>
       </c>
@@ -2929,8 +3464,11 @@
       <c r="F83" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G83" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>164</v>
       </c>
@@ -2949,8 +3487,11 @@
       <c r="F84" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G84" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>166</v>
       </c>
@@ -2969,8 +3510,11 @@
       <c r="F85" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G85" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>168</v>
       </c>
@@ -2989,8 +3533,11 @@
       <c r="F86" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G86" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>170</v>
       </c>
@@ -3009,8 +3556,11 @@
       <c r="F87" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G87" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>172</v>
       </c>
@@ -3029,8 +3579,11 @@
       <c r="F88" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G88" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>174</v>
       </c>
@@ -3049,8 +3602,11 @@
       <c r="F89" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G89" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>176</v>
       </c>
@@ -3069,8 +3625,11 @@
       <c r="F90" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G90" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>178</v>
       </c>
@@ -3089,8 +3648,11 @@
       <c r="F91" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G91" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>180</v>
       </c>
@@ -3109,8 +3671,11 @@
       <c r="F92" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G92" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>182</v>
       </c>
@@ -3129,8 +3694,11 @@
       <c r="F93" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G93" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>184</v>
       </c>
@@ -3149,8 +3717,11 @@
       <c r="F94" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G94" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>186</v>
       </c>
@@ -3169,8 +3740,11 @@
       <c r="F95" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G95" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>188</v>
       </c>
@@ -3189,8 +3763,11 @@
       <c r="F96" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G96" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>190</v>
       </c>
@@ -3209,8 +3786,11 @@
       <c r="F97" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G97" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>192</v>
       </c>
@@ -3229,8 +3809,11 @@
       <c r="F98" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G98" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>194</v>
       </c>
@@ -3243,8 +3826,11 @@
       <c r="F99" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G99" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
         <v>195</v>
       </c>
@@ -3261,7 +3847,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
         <v>196</v>
       </c>
@@ -3278,7 +3864,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
         <v>197</v>
       </c>
@@ -3295,7 +3881,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
         <v>198</v>
       </c>
@@ -3312,7 +3898,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
         <v>199</v>
       </c>
@@ -3329,7 +3915,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
         <v>200</v>
       </c>
@@ -3346,7 +3932,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
         <v>201</v>
       </c>
@@ -3363,7 +3949,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
         <v>202</v>
       </c>
@@ -3380,7 +3966,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
         <v>203</v>
       </c>
@@ -3397,7 +3983,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
         <v>204</v>
       </c>
@@ -3414,7 +4000,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
         <v>205</v>
       </c>
@@ -3431,7 +4017,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
         <v>206</v>
       </c>
@@ -3448,7 +4034,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
         <v>207</v>
       </c>
